--- a/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>ZUMZ</t>
   </si>
@@ -656,200 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E7" s="2">
         <v>44954</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44590</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44226</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43498</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43134</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42763</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42399</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42035</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41671</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41307</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40936</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>875500</v>
+      </c>
+      <c r="E8" s="3">
         <v>958400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1183900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>990700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1034100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>978600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>927400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>836300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>804200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>811600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>724300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>669400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>555900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>633700</v>
+        <v>594600</v>
       </c>
       <c r="E9" s="3">
+        <v>633300</v>
+      </c>
+      <c r="F9" s="3">
         <v>727100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>640600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>667600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>642700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>617500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>561300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>535600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>524500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>462600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>428100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>354200</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>324700</v>
+        <v>280900</v>
       </c>
       <c r="E10" s="3">
+        <v>325100</v>
+      </c>
+      <c r="F10" s="3">
         <v>456700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>350000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>366600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>335900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>309900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>275000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>268600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>287100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>261800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>241300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>201700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,8 +879,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,9 +921,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,33 +966,36 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>200</v>
+      </c>
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="E14" s="3">
-        <v>100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -985,57 +1005,63 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>2100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>19700</v>
+        <v>21000</v>
       </c>
       <c r="E15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F15" s="3">
         <v>20300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19800</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1049,92 +1075,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>927300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1026100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>893700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>948300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>917500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>878600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>796500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>758000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>740000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>651500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>495600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>31100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>157800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>96900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>85800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>71600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>72800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>68500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>60200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1151,92 +1184,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>54100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>183400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>126500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>116400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>89600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>75700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>68100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>76300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>98600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>93200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>81400</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1276,93 +1316,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="E23" s="3">
         <v>32500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>160500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>102500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>91000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>62300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>40200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>71700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>72000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>70300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>61700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>11400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1402,93 +1451,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>119300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>66900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>26300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>43200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>45900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>119300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>66900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>26300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>43200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>45900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1528,9 +1586,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1546,15 +1607,15 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>8700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>500</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1570,9 +1631,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1612,9 +1676,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1654,93 +1721,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>119300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>66900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>45200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>26800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>45900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1780,98 +1856,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>119300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>66900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>45200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>26800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>45900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E38" s="2">
         <v>44954</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44590</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44226</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43498</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43134</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42763</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42399</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42035</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41671</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41307</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40936</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1888,8 +1973,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1906,260 +1992,279 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E41" s="3">
         <v>52700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>62700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>44100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19800</v>
-      </c>
-      <c r="K41" s="3">
-        <v>43200</v>
       </c>
       <c r="L41" s="3">
         <v>43200</v>
       </c>
       <c r="M41" s="3">
+        <v>43200</v>
+      </c>
+      <c r="N41" s="3">
         <v>19600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E42" s="3">
         <v>120800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>177300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>312900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>207100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>135300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>97900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>32400</v>
       </c>
       <c r="L42" s="3">
         <v>32400</v>
       </c>
       <c r="M42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="N42" s="3">
         <v>97500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>85600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>158000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E43" s="3">
         <v>20600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>12800</v>
       </c>
       <c r="L43" s="3">
         <v>12800</v>
       </c>
       <c r="M43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="N43" s="3">
         <v>10300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11700</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E44" s="3">
         <v>134800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>128700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>134400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>135100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>129300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>125800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>106900</v>
-      </c>
-      <c r="K44" s="3">
-        <v>98300</v>
       </c>
       <c r="L44" s="3">
         <v>98300</v>
       </c>
       <c r="M44" s="3">
+        <v>98300</v>
+      </c>
+      <c r="N44" s="3">
         <v>87200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>77600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>65000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E45" s="3">
         <v>11300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>12200</v>
       </c>
       <c r="L45" s="3">
         <v>12200</v>
       </c>
       <c r="M45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>326600</v>
+      </c>
+      <c r="E46" s="3">
         <v>340200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>447600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>535300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>412600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>327200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>279200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>211400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>198900</v>
       </c>
       <c r="L46" s="3">
         <v>198900</v>
       </c>
       <c r="M46" s="3">
+        <v>198900</v>
+      </c>
+      <c r="N46" s="3">
         <v>229800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>203300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>253500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2197,95 +2302,104 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>2400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>287300</v>
+      </c>
+      <c r="E48" s="3">
         <v>316000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>321600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>365500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>414800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>120500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>128900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>129700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>137200</v>
       </c>
       <c r="L48" s="3">
         <v>137200</v>
       </c>
       <c r="M48" s="3">
+        <v>137200</v>
+      </c>
+      <c r="N48" s="3">
         <v>127300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>115500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>89500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E49" s="3">
         <v>71000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>77500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>79600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>70600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>66000</v>
       </c>
       <c r="L49" s="3">
         <v>66000</v>
       </c>
       <c r="M49" s="3">
+        <v>66000</v>
+      </c>
+      <c r="N49" s="3">
         <v>82200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>85100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2325,9 +2439,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2367,51 +2484,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E52" s="3">
         <v>20700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>12600</v>
       </c>
       <c r="L52" s="3">
         <v>12600</v>
       </c>
       <c r="M52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="N52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9100</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2451,51 +2574,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>664200</v>
+      </c>
+      <c r="E54" s="3">
         <v>747900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>862000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>998400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>914300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>534200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>499500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>426700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>414700</v>
       </c>
       <c r="L54" s="3">
         <v>414700</v>
       </c>
       <c r="M54" s="3">
+        <v>414700</v>
+      </c>
+      <c r="N54" s="3">
         <v>443400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>409100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>362200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2512,8 +2641,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2530,50 +2660,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>40400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>21900</v>
       </c>
       <c r="L57" s="3">
         <v>21900</v>
       </c>
       <c r="M57" s="3">
+        <v>21900</v>
+      </c>
+      <c r="N57" s="3">
         <v>18300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21700</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2605,101 +2739,110 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>105400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>128800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>125700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>111900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>47200</v>
       </c>
       <c r="L59" s="3">
         <v>47200</v>
       </c>
       <c r="M59" s="3">
+        <v>47200</v>
+      </c>
+      <c r="N59" s="3">
         <v>42700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>33800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>145800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>184400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>195500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>159700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>99200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>73600</v>
-      </c>
-      <c r="K60" s="3">
-        <v>69100</v>
       </c>
       <c r="L60" s="3">
         <v>69100</v>
       </c>
       <c r="M60" s="3">
+        <v>69100</v>
+      </c>
+      <c r="N60" s="3">
         <v>61400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>57200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>55600</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2731,59 +2874,65 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>194800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>209300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>250300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>288500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>48600</v>
       </c>
       <c r="L62" s="3">
         <v>48600</v>
       </c>
       <c r="M62" s="3">
+        <v>48600</v>
+      </c>
+      <c r="N62" s="3">
         <v>44800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2823,9 +2972,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2865,9 +3017,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2907,51 +3062,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>340600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>393700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>445800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>448200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>133700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>143600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>119600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>117700</v>
       </c>
       <c r="L66" s="3">
         <v>117700</v>
       </c>
       <c r="M66" s="3">
+        <v>117700</v>
+      </c>
+      <c r="N66" s="3">
         <v>107700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>105700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2968,8 +3129,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3009,9 +3171,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3051,9 +3216,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3093,9 +3261,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3135,51 +3306,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>238700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>301000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>380000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>317200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>256600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>209400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>182600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>177200</v>
       </c>
       <c r="L72" s="3">
         <v>177200</v>
       </c>
       <c r="M72" s="3">
+        <v>177200</v>
+      </c>
+      <c r="N72" s="3">
         <v>216000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>189100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>172700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3219,9 +3396,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3261,9 +3441,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3303,51 +3486,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>407300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>468300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>552600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>466100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>400500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>355900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>307100</v>
-      </c>
-      <c r="K76" s="3">
-        <v>297000</v>
       </c>
       <c r="L76" s="3">
         <v>297000</v>
       </c>
       <c r="M76" s="3">
+        <v>297000</v>
+      </c>
+      <c r="N76" s="3">
         <v>335700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>303400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>272300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3387,98 +3576,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E80" s="2">
         <v>44954</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44590</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44226</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43498</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43134</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42763</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42399</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42035</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41671</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41307</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40936</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>119300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>66900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>45200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>26800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>45900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3495,50 +3693,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E83" s="3">
         <v>21600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>27300</v>
       </c>
       <c r="I83" s="3">
         <v>27300</v>
       </c>
       <c r="J83" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K83" s="3">
         <v>27900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>26600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3578,9 +3780,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3620,9 +3825,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3662,9 +3870,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3704,9 +3915,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3746,51 +3960,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>135000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>138400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>105600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>65400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48500</v>
-      </c>
-      <c r="K89" s="3">
-        <v>89900</v>
       </c>
       <c r="L89" s="3">
         <v>89900</v>
       </c>
       <c r="M89" s="3">
+        <v>89900</v>
+      </c>
+      <c r="N89" s="3">
         <v>66900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>66200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3807,50 +4027,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-35800</v>
       </c>
       <c r="L91" s="3">
         <v>-35800</v>
       </c>
       <c r="M91" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-36000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3890,9 +4114,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3932,51 +4159,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E94" s="3">
         <v>54200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>101600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-110500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-102900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-51500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-49600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-68100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3993,8 +4226,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4034,9 +4268,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4076,9 +4313,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4118,9 +4358,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4160,133 +4403,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-87300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-191400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-15200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-35600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>43400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>1200</v>
       </c>
       <c r="L102" s="3">
         <v>1200</v>
       </c>
       <c r="M102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>ZUMZ</t>
   </si>
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>594600</v>
+        <v>593300</v>
       </c>
       <c r="E9" s="3">
         <v>633300</v>
@@ -822,7 +822,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>280900</v>
+        <v>282200</v>
       </c>
       <c r="E10" s="3">
         <v>325100</v>
@@ -975,8 +975,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>44000</v>
       </c>
       <c r="E14" s="3">
         <v>2100</v>
@@ -1081,8 +1081,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>940300</v>
       </c>
       <c r="E17" s="3">
         <v>927300</v>
@@ -1126,8 +1126,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-64800</v>
       </c>
       <c r="E18" s="3">
         <v>31100</v>
@@ -1190,8 +1190,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>2900</v>
       </c>
       <c r="E20" s="3">
         <v>1400</v>
@@ -1235,8 +1235,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-39100</v>
       </c>
       <c r="E21" s="3">
         <v>54100</v>
@@ -1371,7 +1371,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E24" s="3">
         <v>11400</v>
@@ -1460,8 +1460,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-62600</v>
       </c>
       <c r="E26" s="3">
         <v>21000</v>
@@ -1505,8 +1505,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-62600</v>
       </c>
       <c r="E27" s="3">
         <v>21000</v>
@@ -1730,8 +1730,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-2900</v>
       </c>
       <c r="E32" s="3">
         <v>-1400</v>
@@ -1775,8 +1775,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-62600</v>
       </c>
       <c r="E33" s="3">
         <v>21000</v>
@@ -1865,8 +1865,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-62600</v>
       </c>
       <c r="E35" s="3">
         <v>21000</v>
@@ -1999,7 +1999,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>88900</v>
+        <v>49500</v>
       </c>
       <c r="E41" s="3">
         <v>52700</v>
@@ -2044,7 +2044,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>82700</v>
+        <v>122100</v>
       </c>
       <c r="E42" s="3">
         <v>120800</v>
@@ -2666,8 +2666,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>38900</v>
       </c>
       <c r="E57" s="3">
         <v>40400</v>
@@ -2756,8 +2756,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>105200</v>
       </c>
       <c r="E59" s="3">
         <v>105400</v>
@@ -2801,8 +2801,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>8</v>
+      <c r="D60" s="3">
+        <v>144100</v>
       </c>
       <c r="E60" s="3">
         <v>145800</v>
@@ -2891,8 +2891,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>166900</v>
       </c>
       <c r="E62" s="3">
         <v>194800</v>
@@ -3071,8 +3071,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>8</v>
+      <c r="D66" s="3">
+        <v>311000</v>
       </c>
       <c r="E66" s="3">
         <v>340600</v>
@@ -3315,8 +3315,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>176100</v>
       </c>
       <c r="E72" s="3">
         <v>238700</v>
@@ -3495,8 +3495,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>8</v>
+      <c r="D76" s="3">
+        <v>353200</v>
       </c>
       <c r="E76" s="3">
         <v>407300</v>
@@ -3635,8 +3635,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-62600</v>
       </c>
       <c r="E81" s="3">
         <v>21000</v>

--- a/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>ZUMZ</t>
   </si>
@@ -979,7 +979,7 @@
         <v>44000</v>
       </c>
       <c r="E14" s="3">
-        <v>2100</v>
+        <v>-1500</v>
       </c>
       <c r="F14" s="3">
         <v>100</v>
@@ -1082,25 +1082,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>940300</v>
+        <v>896200</v>
       </c>
       <c r="E17" s="3">
-        <v>927300</v>
+        <v>928800</v>
       </c>
       <c r="F17" s="3">
-        <v>1026100</v>
+        <v>1026000</v>
       </c>
       <c r="G17" s="3">
-        <v>893700</v>
+        <v>892300</v>
       </c>
       <c r="H17" s="3">
-        <v>948300</v>
+        <v>948100</v>
       </c>
       <c r="I17" s="3">
-        <v>917500</v>
+        <v>915900</v>
       </c>
       <c r="J17" s="3">
-        <v>878600</v>
+        <v>877000</v>
       </c>
       <c r="K17" s="3">
         <v>796500</v>
@@ -1127,25 +1127,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-64800</v>
+        <v>-20800</v>
       </c>
       <c r="E18" s="3">
-        <v>31100</v>
+        <v>29600</v>
       </c>
       <c r="F18" s="3">
-        <v>157800</v>
+        <v>157900</v>
       </c>
       <c r="G18" s="3">
-        <v>96900</v>
+        <v>98300</v>
       </c>
       <c r="H18" s="3">
-        <v>85800</v>
+        <v>86000</v>
       </c>
       <c r="I18" s="3">
-        <v>61100</v>
+        <v>62700</v>
       </c>
       <c r="J18" s="3">
-        <v>48800</v>
+        <v>50400</v>
       </c>
       <c r="K18" s="3">
         <v>39700</v>
@@ -1191,25 +1191,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2900</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
-        <v>2700</v>
+        <v>900</v>
       </c>
       <c r="G20" s="3">
-        <v>5500</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>5200</v>
+        <v>-1500</v>
       </c>
       <c r="I20" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>-400</v>
+        <v>900</v>
       </c>
       <c r="K20" s="3">
         <v>500</v>
@@ -1236,25 +1236,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-39100</v>
+        <v>-400</v>
       </c>
       <c r="E21" s="3">
-        <v>54100</v>
+        <v>48700</v>
       </c>
       <c r="F21" s="3">
-        <v>183400</v>
+        <v>177300</v>
       </c>
       <c r="G21" s="3">
-        <v>126500</v>
+        <v>122700</v>
       </c>
       <c r="H21" s="3">
-        <v>116400</v>
+        <v>111500</v>
       </c>
       <c r="I21" s="3">
-        <v>89600</v>
+        <v>87200</v>
       </c>
       <c r="J21" s="3">
-        <v>75700</v>
+        <v>74900</v>
       </c>
       <c r="K21" s="3">
         <v>68100</v>
@@ -1280,26 +1280,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1386,10 +1386,10 @@
         <v>24100</v>
       </c>
       <c r="I24" s="3">
-        <v>25800</v>
+        <v>17100</v>
       </c>
       <c r="J24" s="3">
-        <v>22100</v>
+        <v>21600</v>
       </c>
       <c r="K24" s="3">
         <v>14300</v>
@@ -1476,10 +1476,10 @@
         <v>66900</v>
       </c>
       <c r="I26" s="3">
-        <v>36500</v>
+        <v>45200</v>
       </c>
       <c r="J26" s="3">
-        <v>26300</v>
+        <v>26800</v>
       </c>
       <c r="K26" s="3">
         <v>25900</v>
@@ -1521,10 +1521,10 @@
         <v>66900</v>
       </c>
       <c r="I27" s="3">
-        <v>36500</v>
+        <v>45200</v>
       </c>
       <c r="J27" s="3">
-        <v>26300</v>
+        <v>26800</v>
       </c>
       <c r="K27" s="3">
         <v>25900</v>
@@ -1595,26 +1595,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1731,25 +1731,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2900</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-1400</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
-        <v>-2700</v>
+        <v>-900</v>
       </c>
       <c r="G32" s="3">
-        <v>-5500</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-5200</v>
+        <v>1500</v>
       </c>
       <c r="I32" s="3">
-        <v>-1300</v>
+        <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>400</v>
+        <v>-900</v>
       </c>
       <c r="K32" s="3">
         <v>-500</v>
@@ -1999,22 +1999,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>49500</v>
+        <v>88900</v>
       </c>
       <c r="E41" s="3">
-        <v>52700</v>
+        <v>81500</v>
       </c>
       <c r="F41" s="3">
         <v>117200</v>
       </c>
       <c r="G41" s="3">
-        <v>62700</v>
+        <v>73600</v>
       </c>
       <c r="H41" s="3">
-        <v>44100</v>
+        <v>52400</v>
       </c>
       <c r="I41" s="3">
-        <v>30000</v>
+        <v>52400</v>
       </c>
       <c r="J41" s="3">
         <v>24000</v>
@@ -2044,22 +2044,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>122100</v>
+        <v>82700</v>
       </c>
       <c r="E42" s="3">
-        <v>120800</v>
+        <v>92000</v>
       </c>
       <c r="F42" s="3">
         <v>177300</v>
       </c>
       <c r="G42" s="3">
-        <v>312900</v>
+        <v>301900</v>
       </c>
       <c r="H42" s="3">
-        <v>207100</v>
+        <v>198800</v>
       </c>
       <c r="I42" s="3">
-        <v>135300</v>
+        <v>112900</v>
       </c>
       <c r="J42" s="3">
         <v>97900</v>
@@ -2178,26 +2178,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>12400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>11300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>14800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>14400</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>13100</v>
@@ -2268,26 +2268,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2494,25 +2494,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20800</v>
+        <v>12200</v>
       </c>
       <c r="E52" s="3">
-        <v>20700</v>
+        <v>12500</v>
       </c>
       <c r="F52" s="3">
-        <v>20500</v>
+        <v>11800</v>
       </c>
       <c r="G52" s="3">
-        <v>20100</v>
+        <v>10200</v>
       </c>
       <c r="H52" s="3">
-        <v>15200</v>
+        <v>7200</v>
       </c>
       <c r="I52" s="3">
-        <v>12400</v>
+        <v>5800</v>
       </c>
       <c r="J52" s="3">
-        <v>11900</v>
+        <v>6100</v>
       </c>
       <c r="K52" s="3">
         <v>15100</v>
@@ -2712,19 +2712,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>65500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>63600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>61800</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2757,25 +2757,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>105200</v>
+        <v>11400</v>
       </c>
       <c r="E59" s="3">
-        <v>105400</v>
+        <v>11900</v>
       </c>
       <c r="F59" s="3">
-        <v>128800</v>
+        <v>21100</v>
       </c>
       <c r="G59" s="3">
-        <v>125700</v>
+        <v>17200</v>
       </c>
       <c r="H59" s="3">
-        <v>111900</v>
+        <v>14900</v>
       </c>
       <c r="I59" s="3">
-        <v>57800</v>
+        <v>24800</v>
       </c>
       <c r="J59" s="3">
-        <v>61400</v>
+        <v>28100</v>
       </c>
       <c r="K59" s="3">
         <v>48100</v>
@@ -2847,19 +2847,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>159900</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>188800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>204300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>246100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>284700</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2892,19 +2892,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>166900</v>
+        <v>7100</v>
       </c>
       <c r="E62" s="3">
-        <v>194800</v>
+        <v>5900</v>
       </c>
       <c r="F62" s="3">
-        <v>209300</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="3">
-        <v>250300</v>
+        <v>4200</v>
       </c>
       <c r="H62" s="3">
-        <v>288500</v>
+        <v>3700</v>
       </c>
       <c r="I62" s="3">
         <v>40600</v>
@@ -3706,19 +3706,19 @@
         <v>21600</v>
       </c>
       <c r="F83" s="3">
-        <v>22900</v>
+        <v>22800</v>
       </c>
       <c r="G83" s="3">
-        <v>24100</v>
+        <v>24000</v>
       </c>
       <c r="H83" s="3">
-        <v>25400</v>
+        <v>25300</v>
       </c>
       <c r="I83" s="3">
-        <v>27300</v>
+        <v>27200</v>
       </c>
       <c r="J83" s="3">
-        <v>27300</v>
+        <v>27200</v>
       </c>
       <c r="K83" s="3">
         <v>27900</v>
@@ -3982,7 +3982,7 @@
         <v>138400</v>
       </c>
       <c r="H89" s="3">
-        <v>105600</v>
+        <v>106100</v>
       </c>
       <c r="I89" s="3">
         <v>65400</v>
@@ -4515,7 +4515,7 @@
         <v>21700</v>
       </c>
       <c r="H102" s="3">
-        <v>4300</v>
+        <v>4700</v>
       </c>
       <c r="I102" s="3">
         <v>28500</v>

--- a/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>ZUMZ</t>
   </si>
@@ -656,213 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45325</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44954</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44590</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44226</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43498</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43134</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42763</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42399</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42035</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41671</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41307</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40936</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>889200</v>
+      </c>
+      <c r="E8" s="3">
         <v>875500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>958400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1183900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>990700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1034100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>978600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>927400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>836300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>804200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>811600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>724300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>669400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>555900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>585600</v>
+      </c>
+      <c r="E9" s="3">
         <v>593300</v>
       </c>
-      <c r="E9" s="3">
-        <v>633300</v>
-      </c>
       <c r="F9" s="3">
+        <v>633700</v>
+      </c>
+      <c r="G9" s="3">
         <v>727100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>640600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>667600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>642700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>617500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>561300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>535600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>524500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>462600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>428100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>354200</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E10" s="3">
         <v>282200</v>
       </c>
-      <c r="E10" s="3">
-        <v>325100</v>
-      </c>
       <c r="F10" s="3">
+        <v>324700</v>
+      </c>
+      <c r="G10" s="3">
         <v>456700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>350000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>366600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>335900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>309900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>275000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>268600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>287100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>261800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>241300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>201700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -880,8 +892,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -924,9 +937,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -969,36 +985,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>44000</v>
       </c>
-      <c r="E14" s="3">
-        <v>-1500</v>
-      </c>
       <c r="F14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1008,60 +1027,66 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>2100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E15" s="3">
         <v>21000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19800</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1076,98 +1101,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>885800</v>
+      </c>
+      <c r="E17" s="3">
         <v>896200</v>
       </c>
-      <c r="E17" s="3">
-        <v>928800</v>
-      </c>
       <c r="F17" s="3">
+        <v>929200</v>
+      </c>
+      <c r="G17" s="3">
         <v>1026000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>892300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>948100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>915900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>877000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>796500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>758000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>740000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>651500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>495600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20800</v>
       </c>
-      <c r="E18" s="3">
-        <v>29600</v>
-      </c>
       <c r="F18" s="3">
+        <v>29200</v>
+      </c>
+      <c r="G18" s="3">
         <v>157900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>98300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>86000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>62700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>39700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>68500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>60200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1185,98 +1217,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="E20" s="3">
         <v>600</v>
       </c>
       <c r="F20" s="3">
+        <v>600</v>
+      </c>
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
-        <v>48700</v>
-      </c>
       <c r="F21" s="3">
+        <v>48300</v>
+      </c>
+      <c r="G21" s="3">
         <v>177300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>122700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>111500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>87200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>74900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>68100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>76300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>100800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>98600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>93200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>81400</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1301,8 +1340,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1319,99 +1358,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-61900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>160500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>91000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>62300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>40200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>71700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>72000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>61700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>41200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1454,99 +1502,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-62600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>119300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>76200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>66900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>45200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>43200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>45900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>42200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37400</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-62600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>119300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>76200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>66900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>45200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>45900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1589,9 +1646,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1676,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1634,9 +1694,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1679,9 +1742,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1724,99 +1790,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-600</v>
+        <v>-2100</v>
       </c>
       <c r="E32" s="3">
         <v>-600</v>
       </c>
       <c r="F32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-62600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>119300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>76200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>66900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>45200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>45900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1859,104 +1934,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-62600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>119300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>76200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>66900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>45200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>45900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45325</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44954</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44590</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44226</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43498</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43134</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42763</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42399</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42035</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41671</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41307</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40936</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1974,8 +2058,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1993,188 +2078,201 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E41" s="3">
         <v>88900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>81500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73600</v>
-      </c>
-      <c r="H41" s="3">
-        <v>52400</v>
       </c>
       <c r="I41" s="3">
         <v>52400</v>
       </c>
       <c r="J41" s="3">
+        <v>52400</v>
+      </c>
+      <c r="K41" s="3">
         <v>24000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19800</v>
-      </c>
-      <c r="L41" s="3">
-        <v>43200</v>
       </c>
       <c r="M41" s="3">
         <v>43200</v>
       </c>
       <c r="N41" s="3">
+        <v>43200</v>
+      </c>
+      <c r="O41" s="3">
         <v>19600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E42" s="3">
         <v>82700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>177300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>301900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>198800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>112900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59000</v>
-      </c>
-      <c r="L42" s="3">
-        <v>32400</v>
       </c>
       <c r="M42" s="3">
         <v>32400</v>
       </c>
       <c r="N42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="O42" s="3">
         <v>97500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>85600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>158000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E43" s="3">
         <v>13800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>12800</v>
       </c>
       <c r="M43" s="3">
         <v>12800</v>
       </c>
       <c r="N43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="O43" s="3">
         <v>10300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11700</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E44" s="3">
         <v>128800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>134800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>128700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>134400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>135100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>129300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>125800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>106900</v>
-      </c>
-      <c r="L44" s="3">
-        <v>98300</v>
       </c>
       <c r="M44" s="3">
         <v>98300</v>
       </c>
       <c r="N44" s="3">
+        <v>98300</v>
+      </c>
+      <c r="O44" s="3">
         <v>87200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>77600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>65000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2199,72 +2297,78 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>13100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>12200</v>
       </c>
       <c r="M45" s="3">
         <v>12200</v>
       </c>
       <c r="N45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="O45" s="3">
         <v>15200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>322400</v>
+      </c>
+      <c r="E46" s="3">
         <v>326600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>340200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>447600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>535300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>412600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>327200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>279200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>211400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>198900</v>
       </c>
       <c r="M46" s="3">
         <v>198900</v>
       </c>
       <c r="N46" s="3">
+        <v>198900</v>
+      </c>
+      <c r="O46" s="3">
         <v>229800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>203300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>253500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2280,18 +2384,18 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>1700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1600</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2305,101 +2409,110 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E48" s="3">
         <v>287300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>316000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>321600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>365500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>414800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>120500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>128900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>129700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>137200</v>
       </c>
       <c r="M48" s="3">
         <v>137200</v>
       </c>
       <c r="N48" s="3">
+        <v>137200</v>
+      </c>
+      <c r="O48" s="3">
         <v>127300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>115500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>89500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E49" s="3">
         <v>29600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>77500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>79600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>70600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>66000</v>
       </c>
       <c r="M49" s="3">
         <v>66000</v>
       </c>
       <c r="N49" s="3">
+        <v>66000</v>
+      </c>
+      <c r="O49" s="3">
         <v>82200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>85100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2442,9 +2555,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2487,54 +2603,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E52" s="3">
         <v>12200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>12600</v>
       </c>
       <c r="M52" s="3">
         <v>12600</v>
       </c>
       <c r="N52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9100</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2577,54 +2699,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>634900</v>
+      </c>
+      <c r="E54" s="3">
         <v>664200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>747900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>862000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>998400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>914300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>534200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>499500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>426700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>414700</v>
       </c>
       <c r="M54" s="3">
         <v>414700</v>
       </c>
       <c r="N54" s="3">
+        <v>414700</v>
+      </c>
+      <c r="O54" s="3">
         <v>443400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>409100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>362200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2642,8 +2770,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2661,74 +2790,78 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E57" s="3">
         <v>38900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>40400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>21900</v>
       </c>
       <c r="M57" s="3">
         <v>21900</v>
       </c>
       <c r="N57" s="3">
+        <v>21900</v>
+      </c>
+      <c r="O57" s="3">
         <v>18300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>21700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E58" s="3">
         <v>60900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>65500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>61800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2742,128 +2875,137 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>47200</v>
       </c>
       <c r="M59" s="3">
         <v>47200</v>
       </c>
       <c r="N59" s="3">
+        <v>47200</v>
+      </c>
+      <c r="O59" s="3">
         <v>42700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>33800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E60" s="3">
         <v>144100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>145800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>184400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>195500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>159700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>93100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>99200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>73600</v>
-      </c>
-      <c r="L60" s="3">
-        <v>69100</v>
       </c>
       <c r="M60" s="3">
         <v>69100</v>
       </c>
       <c r="N60" s="3">
+        <v>69100</v>
+      </c>
+      <c r="O60" s="3">
         <v>61400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>57200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>55600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>143800</v>
+      </c>
+      <c r="E61" s="3">
         <v>159900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>188800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>204300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>246100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>284700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2877,62 +3019,68 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E62" s="3">
         <v>7100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>48600</v>
       </c>
       <c r="M62" s="3">
         <v>48600</v>
       </c>
       <c r="N62" s="3">
+        <v>48600</v>
+      </c>
+      <c r="O62" s="3">
         <v>44800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2975,9 +3123,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3020,9 +3171,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3065,54 +3219,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>305900</v>
+      </c>
+      <c r="E66" s="3">
         <v>311000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>340600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>393700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>445800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>448200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>133700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>143600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>119600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>117700</v>
       </c>
       <c r="M66" s="3">
         <v>117700</v>
       </c>
       <c r="N66" s="3">
+        <v>117700</v>
+      </c>
+      <c r="O66" s="3">
         <v>107700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>105700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>89900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3130,8 +3290,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3174,9 +3335,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3219,9 +3383,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3264,9 +3431,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3309,54 +3479,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E72" s="3">
         <v>176100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>238700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>301000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>380000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>317200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>256600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>209400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>182600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>177200</v>
       </c>
       <c r="M72" s="3">
         <v>177200</v>
       </c>
       <c r="N72" s="3">
+        <v>177200</v>
+      </c>
+      <c r="O72" s="3">
         <v>216000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>189100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>172700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3399,9 +3575,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3444,9 +3623,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3489,54 +3671,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E76" s="3">
         <v>353200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>407300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>468300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>552600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>466100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>400500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>355900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>307100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>297000</v>
       </c>
       <c r="M76" s="3">
         <v>297000</v>
       </c>
       <c r="N76" s="3">
+        <v>297000</v>
+      </c>
+      <c r="O76" s="3">
         <v>335700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>303400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>272300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3579,104 +3767,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45325</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44954</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44590</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44226</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43498</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43134</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42763</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42399</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42035</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41671</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41307</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40936</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-62600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>119300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>76200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>66900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>45200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>45900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3694,53 +3891,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E83" s="3">
         <v>22800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>27200</v>
       </c>
       <c r="J83" s="3">
         <v>27200</v>
       </c>
       <c r="K83" s="3">
+        <v>27200</v>
+      </c>
+      <c r="L83" s="3">
         <v>27900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>26600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3783,9 +3984,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3828,9 +4032,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3873,9 +4080,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3918,9 +4128,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3963,54 +4176,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E89" s="3">
         <v>14800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>135000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>138400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>106100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>48500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>89900</v>
       </c>
       <c r="M89" s="3">
         <v>89900</v>
       </c>
       <c r="N89" s="3">
+        <v>89900</v>
+      </c>
+      <c r="O89" s="3">
         <v>66900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4028,53 +4247,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-35800</v>
       </c>
       <c r="M91" s="3">
         <v>-35800</v>
       </c>
       <c r="N91" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="O91" s="3">
         <v>-36000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4117,9 +4340,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4162,54 +4388,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>54200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>101600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-110500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-102900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-64000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-49600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-68100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4227,8 +4459,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4271,9 +4504,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4316,9 +4552,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4361,9 +4600,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4406,142 +4648,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-87300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-191400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-15200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-22500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3400</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E102" s="3">
         <v>5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-35600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>43400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22900</v>
-      </c>
-      <c r="L102" s="3">
-        <v>1200</v>
       </c>
       <c r="M102" s="3">
         <v>1200</v>
       </c>
       <c r="N102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZUMZ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>ZUMZ</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44590</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44226</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43862</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43498</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43134</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42763</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42399</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42035</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41671</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41307</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40936</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>929100</v>
+      </c>
+      <c r="E8" s="3">
         <v>889200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>875500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>958400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1183900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>990700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1034100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>978600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>927400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>836300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>804200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>811600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>724300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>669400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>555900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>596000</v>
+      </c>
+      <c r="E9" s="3">
         <v>585600</v>
       </c>
-      <c r="E9" s="3">
-        <v>593300</v>
-      </c>
       <c r="F9" s="3">
+        <v>594600</v>
+      </c>
+      <c r="G9" s="3">
         <v>633700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>727100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>640600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>667600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>642700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>617500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>561300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>535600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>524500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>462600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>428100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>354200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E10" s="3">
         <v>303600</v>
       </c>
-      <c r="E10" s="3">
-        <v>282200</v>
-      </c>
       <c r="F10" s="3">
+        <v>280900</v>
+      </c>
+      <c r="G10" s="3">
         <v>324700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>456700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>350000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>366600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>335900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>309900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>275000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>268600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>287100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>261800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>241300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>201700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -893,8 +906,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,9 +954,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,39 +1005,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
-        <v>44000</v>
-      </c>
       <c r="F14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1030,63 +1050,69 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E15" s="3">
         <v>20500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>27000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19800</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1102,104 +1128,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>906600</v>
+      </c>
+      <c r="E17" s="3">
         <v>885800</v>
       </c>
-      <c r="E17" s="3">
-        <v>896200</v>
-      </c>
       <c r="F17" s="3">
+        <v>938700</v>
+      </c>
+      <c r="G17" s="3">
         <v>929200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1026000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>892300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>948100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>915900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>877000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>796500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>758000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>740000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>651500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>495600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E18" s="3">
         <v>3500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-20800</v>
-      </c>
       <c r="F18" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="G18" s="3">
         <v>29200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>157900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>98300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>86000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>62700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>39700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>71600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>72800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>60200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1218,104 +1251,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>600</v>
       </c>
       <c r="F20" s="3">
         <v>600</v>
       </c>
       <c r="G20" s="3">
+        <v>600</v>
+      </c>
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E21" s="3">
         <v>21900</v>
       </c>
-      <c r="E21" s="3">
-        <v>-400</v>
-      </c>
       <c r="F21" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="G21" s="3">
         <v>48300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>177300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>122700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>111500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>87200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>74900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>68100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>76300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>100800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>98600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>93200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>81400</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1343,8 +1383,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1361,105 +1401,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-61900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>160500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>102500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>91000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>62300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>48400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>71700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>61700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>17100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1505,105 +1554,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-62600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>119300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>66900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>45200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>43200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>45900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>42200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-62600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>119300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>66900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>45200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>43200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>45900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>42200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1649,9 +1707,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1697,9 +1758,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1745,9 +1809,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1793,105 +1860,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-600</v>
       </c>
       <c r="F32" s="3">
         <v>-600</v>
       </c>
       <c r="G32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-62600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>119300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>76200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>66900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>45200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>45900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>42200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1937,110 +2013,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-62600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>119300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>76200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>66900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>45200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>45900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>42200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44590</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44226</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43862</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43498</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43134</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42763</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42399</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42035</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41671</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41307</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40936</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2059,8 +2144,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2079,200 +2165,213 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E41" s="3">
         <v>112700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>73600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>52400</v>
       </c>
       <c r="J41" s="3">
         <v>52400</v>
       </c>
       <c r="K41" s="3">
+        <v>52400</v>
+      </c>
+      <c r="L41" s="3">
         <v>24000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19800</v>
-      </c>
-      <c r="M41" s="3">
-        <v>43200</v>
       </c>
       <c r="N41" s="3">
         <v>43200</v>
       </c>
       <c r="O41" s="3">
+        <v>43200</v>
+      </c>
+      <c r="P41" s="3">
         <v>19600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E42" s="3">
         <v>34900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>82700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>177300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>301900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>198800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>112900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>97900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59000</v>
-      </c>
-      <c r="M42" s="3">
-        <v>32400</v>
       </c>
       <c r="N42" s="3">
         <v>32400</v>
       </c>
       <c r="O42" s="3">
+        <v>32400</v>
+      </c>
+      <c r="P42" s="3">
         <v>97500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>85600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>158000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>12800</v>
       </c>
       <c r="N43" s="3">
         <v>12800</v>
       </c>
       <c r="O43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="P43" s="3">
         <v>10300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11700</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E44" s="3">
         <v>146600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>128800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>134800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>128700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>134400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>135100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>129300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>125800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>106900</v>
-      </c>
-      <c r="M44" s="3">
-        <v>98300</v>
       </c>
       <c r="N44" s="3">
         <v>98300</v>
       </c>
       <c r="O44" s="3">
+        <v>98300</v>
+      </c>
+      <c r="P44" s="3">
         <v>87200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>77600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>65000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2300,75 +2399,81 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>13100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>12200</v>
       </c>
       <c r="N45" s="3">
         <v>12200</v>
       </c>
       <c r="O45" s="3">
+        <v>12200</v>
+      </c>
+      <c r="P45" s="3">
         <v>15200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E46" s="3">
         <v>322400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>326600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>340200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>447600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>535300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>412600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>327200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>279200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>211400</v>
-      </c>
-      <c r="M46" s="3">
-        <v>198900</v>
       </c>
       <c r="N46" s="3">
         <v>198900</v>
       </c>
       <c r="O46" s="3">
+        <v>198900</v>
+      </c>
+      <c r="P46" s="3">
         <v>229800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>203300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>253500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2387,18 +2492,18 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>1700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1600</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2412,107 +2517,116 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>2400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E48" s="3">
         <v>263400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>287300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>316000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>321600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>365500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>414800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>120500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>128900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>129700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>137200</v>
       </c>
       <c r="N48" s="3">
         <v>137200</v>
       </c>
       <c r="O48" s="3">
+        <v>137200</v>
+      </c>
+      <c r="P48" s="3">
         <v>127300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>115500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>89500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E49" s="3">
         <v>28800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>29600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>77500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>74100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>79600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>70600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>66000</v>
       </c>
       <c r="N49" s="3">
         <v>66000</v>
       </c>
       <c r="O49" s="3">
+        <v>66000</v>
+      </c>
+      <c r="P49" s="3">
         <v>82200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>85100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2558,9 +2672,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2606,57 +2723,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E52" s="3">
         <v>11600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>12600</v>
       </c>
       <c r="N52" s="3">
         <v>12600</v>
       </c>
       <c r="O52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="P52" s="3">
         <v>4000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2702,57 +2825,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>644200</v>
+      </c>
+      <c r="E54" s="3">
         <v>634900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>664200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>747900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>862000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>998400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>914300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>534200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>499500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>426700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>414700</v>
       </c>
       <c r="N54" s="3">
         <v>414700</v>
       </c>
       <c r="O54" s="3">
+        <v>414700</v>
+      </c>
+      <c r="P54" s="3">
         <v>443400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>409100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>362200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2771,8 +2900,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2791,80 +2921,84 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E57" s="3">
         <v>49400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>21900</v>
       </c>
       <c r="N57" s="3">
         <v>21900</v>
       </c>
       <c r="O57" s="3">
+        <v>21900</v>
+      </c>
+      <c r="P57" s="3">
         <v>18300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>21700</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E58" s="3">
         <v>56000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>60900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>63600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>67000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>61800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2878,137 +3012,146 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>300</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E59" s="3">
         <v>15000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>47200</v>
       </c>
       <c r="N59" s="3">
         <v>47200</v>
       </c>
       <c r="O59" s="3">
+        <v>47200</v>
+      </c>
+      <c r="P59" s="3">
         <v>42700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E60" s="3">
         <v>155500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>144100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>145800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>184400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>195500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>159700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>99200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73600</v>
-      </c>
-      <c r="M60" s="3">
-        <v>69100</v>
       </c>
       <c r="N60" s="3">
         <v>69100</v>
       </c>
       <c r="O60" s="3">
+        <v>69100</v>
+      </c>
+      <c r="P60" s="3">
         <v>61400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>57200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>55600</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>145300</v>
+      </c>
+      <c r="E61" s="3">
         <v>143800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>159900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>188800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>204300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>246100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>284700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3022,65 +3165,71 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>1600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E62" s="3">
         <v>6600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>46000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>48600</v>
       </c>
       <c r="N62" s="3">
         <v>48600</v>
       </c>
       <c r="O62" s="3">
+        <v>48600</v>
+      </c>
+      <c r="P62" s="3">
         <v>44800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3126,9 +3275,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3174,9 +3326,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3222,57 +3377,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>319900</v>
+      </c>
+      <c r="E66" s="3">
         <v>305900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>311000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>340600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>393700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>445800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>448200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>133700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>143600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>119600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>117700</v>
       </c>
       <c r="N66" s="3">
         <v>117700</v>
       </c>
       <c r="O66" s="3">
+        <v>117700</v>
+      </c>
+      <c r="P66" s="3">
         <v>107700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>89900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3291,8 +3452,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3338,9 +3500,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3386,9 +3551,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3434,9 +3602,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3482,57 +3653,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E72" s="3">
         <v>149200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>176100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>238700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>301000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>380000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>317200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>256600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>209400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>182600</v>
-      </c>
-      <c r="M72" s="3">
-        <v>177200</v>
       </c>
       <c r="N72" s="3">
         <v>177200</v>
       </c>
       <c r="O72" s="3">
+        <v>177200</v>
+      </c>
+      <c r="P72" s="3">
         <v>216000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>189100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>172700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3578,9 +3755,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3626,9 +3806,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3674,57 +3857,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E76" s="3">
         <v>329000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>353200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>407300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>468300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>552600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>466100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>400500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>355900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>307100</v>
-      </c>
-      <c r="M76" s="3">
-        <v>297000</v>
       </c>
       <c r="N76" s="3">
         <v>297000</v>
       </c>
       <c r="O76" s="3">
+        <v>297000</v>
+      </c>
+      <c r="P76" s="3">
         <v>335700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>303400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>272300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3770,110 +3959,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44590</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44226</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43862</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43498</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43134</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42763</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42399</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42035</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41671</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41307</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40936</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-62600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>119300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>76200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>66900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>45200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>45900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>42200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3892,56 +4090,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E83" s="3">
         <v>22200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>27200</v>
       </c>
       <c r="K83" s="3">
         <v>27200</v>
       </c>
       <c r="L83" s="3">
+        <v>27200</v>
+      </c>
+      <c r="M83" s="3">
         <v>27900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>26600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3987,9 +4189,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4035,9 +4240,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4083,9 +4291,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4131,9 +4342,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4179,57 +4393,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E89" s="3">
         <v>20700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>135000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>138400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>106100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>65500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48500</v>
-      </c>
-      <c r="M89" s="3">
-        <v>89900</v>
       </c>
       <c r="N89" s="3">
         <v>89900</v>
       </c>
       <c r="O89" s="3">
+        <v>89900</v>
+      </c>
+      <c r="P89" s="3">
         <v>66900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>66200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68100</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4248,56 +4468,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-35800</v>
       </c>
       <c r="N91" s="3">
         <v>-35800</v>
       </c>
       <c r="O91" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-36000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4343,9 +4567,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4391,57 +4618,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E94" s="3">
         <v>32600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>54200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>101600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-110500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-102900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-51500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-49600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-68100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4460,8 +4693,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4507,9 +4741,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4555,9 +4792,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4603,9 +4843,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4651,151 +4894,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-87300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-191400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-15200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3400</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E102" s="3">
         <v>27200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-35600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>43400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22900</v>
-      </c>
-      <c r="M102" s="3">
-        <v>1200</v>
       </c>
       <c r="N102" s="3">
         <v>1200</v>
       </c>
       <c r="O102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
